--- a/public/exports-with-coowners/29189625.xlsx
+++ b/public/exports-with-coowners/29189625.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258043</t>
+          <t xml:space="preserve">311258047</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286988</t>
+          <t xml:space="preserve">311286996</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286960</t>
+          <t xml:space="preserve">311286964</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">

--- a/public/exports-with-coowners/29189625.xlsx
+++ b/public/exports-with-coowners/29189625.xlsx
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265936</t>
+          <t xml:space="preserve">311265937</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286963</t>
+          <t xml:space="preserve">311286967</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286990</t>
+          <t xml:space="preserve">311287000</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">

--- a/public/exports-with-coowners/29189625.xlsx
+++ b/public/exports-with-coowners/29189625.xlsx
@@ -6514,7 +6514,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258047</t>
+          <t xml:space="preserve">311258043</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265937</t>
+          <t xml:space="preserve">311265936</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -19789,7 +19789,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286967</t>
+          <t xml:space="preserve">311286963</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286996</t>
+          <t xml:space="preserve">311286988</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286964</t>
+          <t xml:space="preserve">311286960</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287000</t>
+          <t xml:space="preserve">311286990</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
